--- a/artfynd/A 36627-2022 artfynd.xlsx
+++ b/artfynd/A 36627-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 36627-2022 artfynd.xlsx
+++ b/artfynd/A 36627-2022 artfynd.xlsx
@@ -675,43 +675,43 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>97045507</v>
+        <v>97045571</v>
       </c>
       <c r="B2" t="n">
-        <v>100515</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5173</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>223246</v>
+        <v>102185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Myskbock</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Aromia moschata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Huds.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>434489.3364682792</v>
+        <v>434490</v>
       </c>
       <c r="R2" t="n">
-        <v>6471586.502204164</v>
+        <v>6471587</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -752,24 +752,9 @@
           <t>2021-08-19</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-08-19</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Grovt och friskt träd</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -797,15 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>97045571</v>
+        <v>97045566</v>
       </c>
       <c r="B3" t="n">
-        <v>5107</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58085</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -813,30 +793,29 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102185</v>
+        <v>205976</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Myskbock</t>
+          <t>Gråkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Aromia moschata</t>
+          <t>Corvus corone cornix</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -846,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>434489.3364682792</v>
+        <v>434490</v>
       </c>
       <c r="R3" t="n">
-        <v>6471586.502204164</v>
+        <v>6471587</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,19 +858,9 @@
           <t>2021-08-19</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-08-19</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -900,7 +869,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -919,47 +887,38 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>97045566</v>
+        <v>97045507</v>
       </c>
       <c r="B4" t="n">
-        <v>56521</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>103403</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103035</v>
+        <v>223246</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kråka</t>
+          <t>Skogsalm</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Corvus corone</t>
+          <t>Ulmus glabra</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Huds.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -967,10 +926,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>434489.3364682792</v>
+        <v>434490</v>
       </c>
       <c r="R4" t="n">
-        <v>6471586.502204164</v>
+        <v>6471587</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1000,19 +959,14 @@
           <t>2021-08-19</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2021-08-19</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Grovt och friskt träd</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,6 +975,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 36627-2022 artfynd.xlsx
+++ b/artfynd/A 36627-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97045571</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97045566</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -991,8 +1006,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97045507</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>